--- a/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.WS.RPR.04.01. Kuru işlem Günlük Üretim Raporu.xlsx
+++ b/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.WS.RPR.04.01. Kuru işlem Günlük Üretim Raporu.xlsx
@@ -300,7 +300,7 @@
 تاريخ آخر تعديل</t>
   </si>
   <si>
-    <t>EG.WS.RPR.04.01</t>
+    <t>EMS.WS.RPR.04.01</t>
   </si>
 </sst>
 </file>
